--- a/www/download/IND.gdp.s.du.zdW13.xlsx
+++ b/www/download/IND.gdp.s.du.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65489.5702733134</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66073.3105511098</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66525.4910418564</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66500.1198687319</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70390.3440215755</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72556.3757791087</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70403.5314688487</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72591.2544603571</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79373.7461041282</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88353.4489293888</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97387.6911739028</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104766.093102546</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121247.701789399</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143404.124380168</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140638.093859911</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29875.1318830344</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29988.8948288225</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30048.3799216018</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29734.0252825739</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30754.6407540154</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31382.3827003868</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30465.7120648172</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30789.8435748066</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33107.4224163394</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36507.8517236433</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38491.1611075629</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40113.2213750378</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45434.8056476236</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50790.1305199459</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44192.9542835859</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22789.5683074509</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22662.5939982593</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22684.4085747658</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22606.9210175435</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23740.7586789752</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24658.5860825102</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24044.4762835432</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24100.5982202833</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25661.4172636123</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28224.4111718515</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29938.7846729403</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31577.2777754955</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35984.3946261532</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39624.5098825539</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36154.0248277153</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34866.7740127224</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35607.677201446</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34383.3435262634</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32592.0983691085</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32029.4795810262</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31263.9017713637</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29239.4390575032</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29848.7495322741</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32091.9982242635</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36246.7161200586</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39596.4415338551</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42637.0002312147</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49117.3830728636</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53005.515300034</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48140.3440864817</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>742836.955369213</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>727881.164058284</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>734183.390017631</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>713519.65545716</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>772127.306796667</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>790055.837638853</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>759316.16897094</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>798711.669091198</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>865610.222072671</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>1003026.24739715</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1090579.66803315</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1136813.17516639</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>1300855.06542312</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1462502.30673197</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.341</t>
+          <t>1341295.13870408</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95183.267365107</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97023.9886869</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98322.1015839428</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97763.7399109706</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103116.873476462</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106687.505637475</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102309.331436922</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105089.28883462</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113594.149278158</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128284.732372413</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138033.590054225</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145566.015323487</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166454.795719396</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182717.355585424</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166172.58750972</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.991</t>
+          <t>7990560.71270913</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8070064.15778069</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8.075</t>
+          <t>8075345.83209919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7.967</t>
+          <t>7966801.95715463</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.353</t>
+          <t>8353120.60962133</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.584</t>
+          <t>8584419.71436284</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8.498</t>
+          <t>8497599.95770357</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.887</t>
+          <t>8887265.66716479</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9.696</t>
+          <t>9696486.06941191</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10.808</t>
+          <t>10808013.6795989</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11.615</t>
+          <t>11614515.4559062</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12.492</t>
+          <t>12492148.7592579</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>14.372</t>
+          <t>14371972.8954692</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>16.184</t>
+          <t>16184482.2090982</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15.125</t>
+          <t>15125484.0716397</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2269.93322256982</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2255.05747598861</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2233.12484983342</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2207.44588619155</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2300.92269805809</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2344.29418278861</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2290.0975590877</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2339.14439238457</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2594.37691705569</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2901.23514942588</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3123.40453925988</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3298.89918350412</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3782.68653840042</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4071.02308653699</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3841.83874355888</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55167.9482257242</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56279.4253383693</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55765.5278437432</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54167.4775688337</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54206.6474530312</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54246.7569686002</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50614.9407015455</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50856.449973337</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53345.8645435553</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58890.2676660114</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63760.038652336</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67397.0626114771</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77142.8882038948</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86275.4628519997</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75812.6004287191</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263186.706702958</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256541.652087</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251990.413214862</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249871.577758975</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257450.663667416</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259877.850091066</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248029.778496949</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248059.894735753</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261070.664426467</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287950.786454954</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304180.712637593</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>317073.389848181</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>361632.215859361</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>395257.163424851</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356195.52082517</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19232.6558099013</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19215.3444356004</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19505.5219949219</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19729.6974728457</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20649.9876919682</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21188.9639425581</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20636.1412453514</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20916.001966868</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21975.6396465143</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23823.741749771</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25600.0633023701</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27258.1457751298</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30895.7420559873</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33992.0153647909</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31183.3324079522</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103895.993299485</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105289.29766103</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108750.030148009</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112112.69194758</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121833.064906697</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129738.217748473</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129245.431951233</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134906.201782814</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147034.23090728</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164343.256383602</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179903.136795652</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192337.799397545</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218950.410813905</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229711.417778493</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190954.407736073</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6738.95629945707</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6535.80011476356</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6406.57745778851</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6129.7941083308</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5934.91083261365</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5833.5549044471</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5758.67653863467</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5843.27226363361</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6556.8438728977</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7431.71952409887</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7898.72486390496</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8747.98446501913</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10029.5351365387</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10761.8316397662</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8314.4291979654</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19013.961220811</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19198.6563660836</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19686.3565514329</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19671.0149612969</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20887.7505218821</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21314.6462007086</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20588.6836875391</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20979.7075330204</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22206.8299499886</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24459.4914617889</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26308.7565671792</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27869.3281377024</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31883.3435041947</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35301.8686417381</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31094.5480180054</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151736.04581515</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152511.471490516</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150411.817896286</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148319.087410317</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155236.382324564</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155990.573860685</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151384.968680495</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151115.476807171</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161100.091134943</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179989.063523719</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192800.401608564</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201630.828322423</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232774.563238227</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>258043.390206489</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231895.175857373</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181988.364508078</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183135.597401853</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183884.793603462</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181994.198135187</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186968.727819349</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188206.517074552</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182085.262476635</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184180.38345137</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>195757.659161512</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215219.312901132</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232186.163221626</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>242289.958805259</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272959.116954676</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294875.129622306</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>269207.566491166</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39656.1322202637</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39433.6516453734</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37739.3455635223</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38156.7167801369</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40585.9360873487</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40891.7184411501</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39201.4616673779</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39254.8161637668</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41753.8878951156</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45260.8616201562</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48287.8422906401</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52716.3840743559</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59542.7282684334</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63216.8386545532</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60769.7178222758</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44884.9947622918</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45125.5594050046</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45050.9265337583</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45404.8858252135</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48190.7386160554</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49025.7160468492</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46127.1273781542</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47105.3505349617</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48954.5693104334</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53039.3034746443</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55230.8796236343</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57758.416037436</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64626.4624381763</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66776.4277359201</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61600.4827849778</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>749226.867337211</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>758800.080540515</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>730241.997551579</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>743591.531167578</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>839843.300922625</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>914922.096323871</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898156.769525196</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>960746.490742457</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1055918.46400815</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1170673.1522909</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1133911.67141279</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1104843.88992785</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1278571.2512828</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.411</t>
+          <t>1410873.35617388</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1336677.58605067</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6230365.16371026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.484</t>
+          <t>6484441.71023567</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6.512</t>
+          <t>6512267.34366374</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6.482</t>
+          <t>6481617.7776919</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.645</t>
+          <t>6644779.24123708</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7079764.39695681</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.146</t>
+          <t>7146478.48845754</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>7.144</t>
+          <t>7144154.0231807</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8070499.54908486</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>9.101</t>
+          <t>9100849.95883467</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10.051</t>
+          <t>10051397.4547493</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>10.567</t>
+          <t>10567145.6156233</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>11.552</t>
+          <t>11551753.3414925</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>12.697</t>
+          <t>12696674.1559368</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11.862</t>
+          <t>11861756.8638244</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12769.3531340179</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13286.7918207544</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13700.5462858057</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14180.6555329346</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15453.6633605687</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16274.6656109933</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16243.5247434164</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16549.0694282202</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17908.6792919374</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20207.001378493</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22587.0263552253</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24745.367021709</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28306.547945696</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31258.5017232113</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26492.7994769919</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175773.02924986</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176565.261684106</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176203.302166586</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177108.170767099</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183525.285307883</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184663.045186097</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>180947.782733426</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184668.094892894</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197528.057251104</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218810.454788617</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234118.57920054</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247954.622189121</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>283013.429138381</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307390.037598834</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271534.29954086</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>584463.523138019</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588027.031750674</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>580990.368821953</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>550126.216910871</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>557335.139223971</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564114.590034197</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>535767.660187832</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>531698.573557224</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>568977.090196146</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>622205.929159605</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>654757.014005757</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>687668.689792028</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>776109.637344949</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>821827.388920509</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>705991.267971383</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246595.676929233</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>241444.550871335</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236912.928002541</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215598.901735419</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>230294.888016164</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240562.440774902</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229817.945337322</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235374.541407637</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>253567.431489375</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289197.749140231</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>297020.912802019</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>309007.907017917</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>339648.713718512</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374121.702891824</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>347706.782081322</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15028.2390925972</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15215.8253999373</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14696.9413391798</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15290.8481334126</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14975.8321912235</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15496.0228024728</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14324.2676312429</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14680.1721388314</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16093.6877497649</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17477.5523476409</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19710.3299616258</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20150.0964480615</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23402.399299415</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24829.6562805292</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21176.7336637414</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1362.04982508153</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1403.68187857233</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1436.97278701064</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1453.88857447691</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1507.74867619747</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1617.89822782185</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1623.34460608532</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1719.34024194021</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1982.99334946774</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2235.41336166957</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2451.07347949343</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2624.10695760298</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3048.47237912677</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3592.23933900463</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3369.04801905235</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8155.64600635565</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8045.56827642315</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8281.4096942922</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8005.85969881481</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7823.21209444531</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7205.97613238174</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6843.50906610251</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6834.62179918239</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7508.61104303204</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8240.85866184656</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8998.7774712211</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9736.1111485501</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11191.8637107395</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11727.1641296331</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8013.82204903543</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>372717.337044011</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391577.978905594</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>395777.527712445</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>403334.657629665</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>431914.42193895</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>448843.310918647</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>437638.054487718</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>448933.579827613</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496556.638090261</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>569423.715119925</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>608458.146904727</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>644027.204796874</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>727503.286908748</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>861097.567865028</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>786742.646514329</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1133.30492799141</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1146.46184539824</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1147.33872571292</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1151.52582155741</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1213.97877117487</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1247.98262389244</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1044.93947530033</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1260.24715727859</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1249.7033445321</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1379.51420341295</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1446.25323022118</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1523.04710284972</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1713.17823868069</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1785.47769954616</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1635.94538342142</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41583.6299211919</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42335.8913035481</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43148.1441974556</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42792.9343200526</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45419.4989098958</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47220.5162306251</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46403.0088983629</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47590.4264959408</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50749.5254516573</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55043.2454854175</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58584.787021751</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61520.6941269953</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70072.3597817549</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78418.5257341</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72581.505702656</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177972.304193785</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182074.665893292</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182640.077590841</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179659.406102118</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180023.596201044</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179627.227595447</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152238.600539272</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147948.687705995</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155675.308832672</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171794.262438625</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186287.899237632</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>198081.698074504</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>228098.993897106</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259420.687433146</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233277.521719337</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43766.2816179869</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44253.3264293625</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44174.3587104257</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44029.5890841894</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46307.7633037824</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48261.7849112804</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46761.0606111631</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47746.098239886</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49715.9024488488</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54151.0091710358</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56799.4497750037</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59574.0641734514</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66828.0597354246</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72052.4378480108</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64867.0813446024</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120799.76634796</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124319.640285593</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117393.818267882</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112182.536568858</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143027.889704432</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143347.093747518</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137397.139363348</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122830.064144151</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129503.289142183</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134430.884389194</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142156.467880755</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148466.160116254</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167797.007287164</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183802.803462434</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166481.192704643</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>955311.888263536</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>935238.990183958</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>889941.810106109</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>835790.552988971</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>869861.671219687</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>891287.499511735</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>861851.437004096</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>874069.650055636</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>932402.345057848</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.023</t>
+          <t>1022845.72961115</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.088</t>
+          <t>1088306.43189674</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1137194.32222135</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1288150.86020785</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1405269.17867328</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1265225.94778558</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22337.514098888</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21973.5100343781</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21504.3991047202</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20543.2119401833</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20354.3562359229</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20031.6205751085</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19099.7984385538</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18551.4562154549</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19385.3661863679</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21843.9384261011</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23305.6728292831</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23992.7371721337</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27983.9008720025</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32079.326767616</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28645.09844526</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10100.0194031466</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9754.33533018511</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9517.13813510647</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9282.16609556519</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9616.72238000603</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9756.2141047764</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9425.65515715225</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9503.49364346187</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10030.9064292164</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10936.0496957881</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11664.8198915551</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12186.6749583869</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13996.0628087658</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16095.1963610001</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14204.4207088353</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33792.4111452511</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33871.4874516718</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33252.7976740022</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33352.6973853618</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35391.4256582544</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36242.6852094568</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35507.3455383301</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35935.6000301882</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37907.1762414717</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41855.6505260942</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44662.4732237633</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46616.2344096636</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54241.3279034626</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60100.9480487012</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54325.2018032456</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275835.969167908</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288997.270005088</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>287394.042083733</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>273469.80042401</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>281760.556052784</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>264238.936405386</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256415.035067755</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251840.486539509</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262641.869131955</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>294131.138554317</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311790.346253837</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>309856.110069807</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>326665.658762243</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>364205.825036117</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>333466.632529567</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108561.136160622</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106766.89208147</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108147.491351681</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105258.830586112</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108240.75712978</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110696.560279864</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99080.6049468584</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100949.356631957</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109035.458232608</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122761.505196849</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133360.220796222</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140340.515378259</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>161433.147409528</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177363.538207521</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155107.997827379</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806944.479800916</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>822733.054312522</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>839260.054884177</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>845463.073807558</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>889011.234381967</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>924305.835560752</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>880840.715356577</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>879701.957490368</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>933620.928238336</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1040320.89089098</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1124436.69521469</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>1203843.28932227</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1355149.21349142</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1454976.33758998</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1273047.04339583</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>11.625</t>
+          <t>11625293.8467547</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11949684.1081556</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12.109</t>
+          <t>12109226.8824011</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12.155</t>
+          <t>12155335.5988199</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>12.849</t>
+          <t>12849095.7108573</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13.583</t>
+          <t>13582748.2125991</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13.623</t>
+          <t>13623494.3588201</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>14.369</t>
+          <t>14368869.4188734</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>16.053</t>
+          <t>16052951.6365496</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>18.169</t>
+          <t>18168549.7184322</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19.874</t>
+          <t>19873893.5679743</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21530437.893548</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>24.493</t>
+          <t>24492854.1643649</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>27630206.5178216</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>26.083</t>
+          <t>26082562.9010511</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>32.489</t>
+          <t>32489263.1092772</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>33.177</t>
+          <t>33176781.4152028</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>33300175.0736809</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>33.076</t>
+          <t>33075903.5367022</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>34.706</t>
+          <t>34706303.6393241</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>36.302</t>
+          <t>36302159.7257576</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>36.047</t>
+          <t>36046742.2333619</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>37.306</t>
+          <t>37306109.2209233</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41239686.2993782</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>46.351</t>
+          <t>46351331.4493274</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>50.278</t>
+          <t>50277928.9881531</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>53.684</t>
+          <t>53683536.7904871</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>60.733</t>
+          <t>60732819.6127407</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>67.874</t>
+          <t>67873977.292048</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>63.338</t>
+          <t>63337837.1748177</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
